--- a/assets/MEK_SALES_TEMPLATE_QT_KR.xlsx
+++ b/assets/MEK_SALES_TEMPLATE_QT_KR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\msm_app\msm_app1\client\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15367702-6F55-4AD7-92FE-0C89AE424279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B98870C-4AA5-40BF-8FFE-F718D9A80714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="1995" windowWidth="28470" windowHeight="13485" tabRatio="963" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57270" yWindow="780" windowWidth="28470" windowHeight="13485" tabRatio="963" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QT_FORM_TEST" sheetId="29" r:id="rId1"/>
@@ -76,10 +76,6 @@
   </si>
   <si>
     <t>품목 내역</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>견 적 서</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -339,6 +335,10 @@
     <t>$(MEKICS_EMP_PHONE_NUM)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>견 적 서sdfdsdsf</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1484,6 +1484,36 @@
     <xf numFmtId="177" fontId="22" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="31" fontId="26" fillId="2" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1522,36 +1552,6 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="2" borderId="1" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="31" fontId="26" fillId="2" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3386,16 +3386,16 @@
       <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:24" ht="35.25">
-      <c r="A2" s="124" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
+      <c r="A2" s="114" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:24" ht="24">
@@ -3410,13 +3410,13 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:24" s="26" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A4" s="123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="123"/>
+      <c r="A4" s="113" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="113"/>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3439,13 +3439,13 @@
       <c r="X4" s="26" ph="1"/>
     </row>
     <row r="5" spans="1:24" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="125" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="125"/>
+      <c r="A5" s="115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="115"/>
       <c r="C5" s="15"/>
       <c r="D5" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -3479,13 +3479,13 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1">
-      <c r="A7" s="123" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="123"/>
+      <c r="A7" s="113" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="113"/>
       <c r="C7" s="11"/>
       <c r="D7" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -3498,7 +3498,7 @@
       <c r="B8" s="20"/>
       <c r="C8" s="21"/>
       <c r="D8" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -3507,10 +3507,10 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:24" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="123" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="123"/>
+      <c r="A9" s="113" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="113"/>
       <c r="C9" s="11"/>
       <c r="D9" s="22">
         <f>H40</f>
@@ -3537,10 +3537,10 @@
       <c r="X9" s="26" ph="1"/>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1">
-      <c r="A10" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="123"/>
+      <c r="A10" s="113" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="113"/>
       <c r="C10" s="11"/>
       <c r="D10" s="28">
         <f>H40</f>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="12" spans="1:24" ht="19.5" customHeight="1" thickBot="1">
       <c r="A12" s="90" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -3589,17 +3589,17 @@
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="J12" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:24" s="26" customFormat="1" ht="19.5" customHeight="1" thickBot="1">
       <c r="A13" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="122"/>
+      <c r="C13" s="112"/>
       <c r="D13" s="30"/>
       <c r="E13" s="77" t="s">
         <v>4</v>
@@ -3634,7 +3634,7 @@
     <row r="14" spans="1:24" ht="19.5" customHeight="1" thickTop="1">
       <c r="A14" s="52"/>
       <c r="B14" s="53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="54"/>
       <c r="D14" s="55"/>
@@ -3642,7 +3642,7 @@
       <c r="F14" s="54"/>
       <c r="G14" s="57"/>
       <c r="H14" s="76" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J14" s="8" t="str">
         <f>IF(A14&gt;0,A14,"")</f>
@@ -3652,7 +3652,7 @@
     <row r="15" spans="1:24" ht="19.5" customHeight="1">
       <c r="A15" s="58"/>
       <c r="B15" s="64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="65"/>
       <c r="D15" s="66"/>
@@ -3668,7 +3668,7 @@
     <row r="16" spans="1:24" ht="19.5" customHeight="1">
       <c r="A16" s="58"/>
       <c r="B16" s="59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" s="60"/>
       <c r="D16" s="93"/>
@@ -3701,14 +3701,14 @@
       </c>
       <c r="B18" s="35"/>
       <c r="C18" s="36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" s="103"/>
       <c r="E18" s="104">
         <v>2</v>
       </c>
       <c r="F18" s="105" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" s="106">
         <v>9900000</v>
@@ -3726,7 +3726,7 @@
       <c r="A19" s="34"/>
       <c r="B19" s="35"/>
       <c r="C19" s="36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" s="103"/>
       <c r="E19" s="104"/>
@@ -3742,7 +3742,7 @@
       <c r="A20" s="34"/>
       <c r="B20" s="35"/>
       <c r="C20" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" s="103"/>
       <c r="E20" s="104"/>
@@ -3772,7 +3772,7 @@
       <c r="A22" s="34"/>
       <c r="B22" s="35"/>
       <c r="C22" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" s="37"/>
       <c r="E22" s="38"/>
@@ -3788,10 +3788,10 @@
       <c r="A23" s="34"/>
       <c r="B23" s="35"/>
       <c r="C23" s="36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" s="38">
         <v>2</v>
@@ -3808,10 +3808,10 @@
       <c r="A24" s="34"/>
       <c r="B24" s="35"/>
       <c r="C24" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" s="38">
         <v>2</v>
@@ -3828,10 +3828,10 @@
       <c r="A25" s="43"/>
       <c r="B25" s="35"/>
       <c r="C25" s="36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" s="38">
         <v>2</v>
@@ -3848,10 +3848,10 @@
       <c r="A26" s="34"/>
       <c r="B26" s="42"/>
       <c r="C26" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="37" t="s">
         <v>39</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>40</v>
       </c>
       <c r="E26" s="38">
         <v>2</v>
@@ -3868,10 +3868,10 @@
       <c r="A27" s="34"/>
       <c r="B27" s="42"/>
       <c r="C27" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E27" s="38">
         <v>2</v>
@@ -3888,10 +3888,10 @@
       <c r="A28" s="34"/>
       <c r="B28" s="35"/>
       <c r="C28" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E28" s="38">
         <v>2</v>
@@ -3908,10 +3908,10 @@
       <c r="A29" s="34"/>
       <c r="B29" s="35"/>
       <c r="C29" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="37" t="s">
         <v>43</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>44</v>
       </c>
       <c r="E29" s="38">
         <v>2</v>
@@ -3928,10 +3928,10 @@
       <c r="A30" s="34"/>
       <c r="B30" s="35"/>
       <c r="C30" s="36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" s="38">
         <v>2</v>
@@ -3948,10 +3948,10 @@
       <c r="A31" s="34"/>
       <c r="B31" s="35"/>
       <c r="C31" s="36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" s="38">
         <v>2</v>
@@ -4049,29 +4049,29 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A38" s="118" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="119"/>
-      <c r="C38" s="119"/>
-      <c r="D38" s="119"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="119"/>
-      <c r="G38" s="120"/>
+      <c r="A38" s="108" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="109"/>
+      <c r="C38" s="109"/>
+      <c r="D38" s="109"/>
+      <c r="E38" s="109"/>
+      <c r="F38" s="109"/>
+      <c r="G38" s="110"/>
       <c r="H38" s="74"/>
       <c r="J38" s="91"/>
       <c r="K38" s="24"/>
       <c r="L38" s="24"/>
     </row>
     <row r="39" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A39" s="111" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="111"/>
-      <c r="C39" s="111"/>
-      <c r="D39" s="111"/>
-      <c r="E39" s="111"/>
-      <c r="F39" s="112"/>
+      <c r="A39" s="119" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="119"/>
+      <c r="C39" s="119"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
       <c r="G39" s="80"/>
       <c r="H39" s="81"/>
       <c r="J39" s="92"/>
@@ -4079,16 +4079,16 @@
       <c r="L39" s="24"/>
     </row>
     <row r="40" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A40" s="115" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" s="115"/>
-      <c r="C40" s="115"/>
-      <c r="D40" s="115"/>
-      <c r="E40" s="115"/>
-      <c r="F40" s="116"/>
+      <c r="A40" s="123" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="123"/>
+      <c r="C40" s="123"/>
+      <c r="D40" s="123"/>
+      <c r="E40" s="123"/>
+      <c r="F40" s="124"/>
       <c r="G40" s="80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H40" s="83">
         <f>SUM(H14:H36)</f>
@@ -4105,76 +4105,76 @@
       <c r="F41" s="84"/>
       <c r="G41" s="85"/>
       <c r="H41" s="86" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:12" ht="19.5" customHeight="1">
+      <c r="A42" s="121" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="121"/>
+      <c r="C42" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="122"/>
+      <c r="E42" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="121"/>
+      <c r="G42" s="125" t="s">
+        <v>2</v>
+      </c>
+      <c r="H42" s="116"/>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:12" ht="19.5" customHeight="1">
+      <c r="A43" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="121"/>
+      <c r="C43" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="J41" s="1"/>
-    </row>
-    <row r="42" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A42" s="113" t="s">
+      <c r="D43" s="122"/>
+      <c r="E43" s="121" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" s="121"/>
+      <c r="G43" s="116" t="s">
+        <v>55</v>
+      </c>
+      <c r="H43" s="116"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:12" ht="19.5" customHeight="1">
+      <c r="A44" s="121" t="s">
         <v>13</v>
       </c>
-      <c r="B42" s="113"/>
-      <c r="C42" s="114" t="s">
-        <v>26</v>
-      </c>
-      <c r="D42" s="114"/>
-      <c r="E42" s="113" t="s">
-        <v>21</v>
-      </c>
-      <c r="F42" s="113"/>
-      <c r="G42" s="117" t="s">
-        <v>2</v>
-      </c>
-      <c r="H42" s="108"/>
-      <c r="J42" s="1"/>
-    </row>
-    <row r="43" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A43" s="113" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="113"/>
-      <c r="C43" s="114" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="114"/>
-      <c r="E43" s="113" t="s">
+      <c r="B44" s="121"/>
+      <c r="C44" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="122"/>
+      <c r="E44" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="F43" s="113"/>
-      <c r="G43" s="108" t="s">
+      <c r="F44" s="121"/>
+      <c r="G44" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="H43" s="108"/>
-      <c r="J43" s="1"/>
-    </row>
-    <row r="44" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A44" s="113" t="s">
-        <v>14</v>
-      </c>
-      <c r="B44" s="113"/>
-      <c r="C44" s="114" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="114"/>
-      <c r="E44" s="113" t="s">
-        <v>23</v>
-      </c>
-      <c r="F44" s="113"/>
-      <c r="G44" s="108" t="s">
-        <v>57</v>
-      </c>
-      <c r="H44" s="108"/>
+      <c r="H44" s="116"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A45" s="109"/>
-      <c r="B45" s="110"/>
-      <c r="C45" s="110"/>
-      <c r="D45" s="110"/>
-      <c r="E45" s="110"/>
-      <c r="F45" s="110"/>
-      <c r="G45" s="110"/>
-      <c r="H45" s="110"/>
+      <c r="A45" s="117"/>
+      <c r="B45" s="118"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="118"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="118"/>
+      <c r="H45" s="118"/>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:12" ht="24">
@@ -4199,14 +4199,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A9:B9"/>
     <mergeCell ref="G44:H44"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A39:F39"/>
@@ -4222,6 +4214,14 @@
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="G43:H43"/>
     <mergeCell ref="E44:F44"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.39" right="0.17" top="0.91" bottom="5.6145833333333332E-2" header="0.3" footer="0.49"/>

--- a/assets/MEK_SALES_TEMPLATE_QT_KR.xlsx
+++ b/assets/MEK_SALES_TEMPLATE_QT_KR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\msm_app\msm_app1\client\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\msm_app\msm_app2_other_version\client\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B98870C-4AA5-40BF-8FFE-F718D9A80714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687873C2-727D-4DB4-8B56-48EC32CB49A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57270" yWindow="780" windowWidth="28470" windowHeight="13485" tabRatio="963" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28470" yWindow="1170" windowWidth="28470" windowHeight="13485" tabRatio="963" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QT_FORM_TEST" sheetId="29" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>지불조건</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -336,8 +336,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>견 적 서sdfdsdsf</t>
+    <t>견 적 서sdfdsdsf_수정함_)0919그대로 가져오기</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdfdfdssfd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -355,7 +359,7 @@
     <numFmt numFmtId="181" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
     <numFmt numFmtId="182" formatCode="[DBNum4][$-412]General"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -534,14 +538,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="굴림"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
       <name val="굴림"/>
       <family val="3"/>
       <charset val="129"/>
@@ -660,6 +656,27 @@
       <b/>
       <sz val="18"/>
       <color rgb="FFFF0000"/>
+      <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="36"/>
+      <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="36"/>
       <name val="굴림"/>
       <family val="3"/>
       <charset val="129"/>
@@ -1126,7 +1143,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1143,13 +1160,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="33" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="32" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="32" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="41" fontId="31" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1188,30 +1205,22 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="26" fillId="2" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1221,14 +1230,6 @@
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="26" fillId="2" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="27" fillId="2" borderId="0" xfId="18" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1382,176 +1383,200 @@
     <xf numFmtId="177" fontId="5" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="4" borderId="1" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="1" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="42" fontId="38" fillId="4" borderId="1" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="42" fontId="37" fillId="4" borderId="1" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="37" fillId="4" borderId="1" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="38" fillId="4" borderId="1" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="42" fontId="37" fillId="2" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="42" fontId="38" fillId="2" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="22" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="22" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="31" fontId="26" fillId="2" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="5" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="5" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="5" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="11" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="1" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="12" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="181" fontId="45" fillId="2" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="45" fillId="2" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="45" fillId="2" borderId="0" xfId="18" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="31" fontId="26" fillId="2" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="5" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="5" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="5" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="11" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="1" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="1" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="12" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="1" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3360,18 +3385,18 @@
   <dimension ref="A1:X47"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="24" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="24" customWidth="1"/>
-    <col min="3" max="3" width="3.875" style="24" customWidth="1"/>
-    <col min="4" max="4" width="52.75" style="24" customWidth="1"/>
-    <col min="5" max="5" width="6.375" style="25" customWidth="1"/>
-    <col min="6" max="6" width="6.5" style="25" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="24" customWidth="1"/>
-    <col min="8" max="8" width="17.875" style="24" customWidth="1"/>
-    <col min="9" max="9" width="2.75" style="24" customWidth="1"/>
-    <col min="10" max="10" width="4.625" style="24" customWidth="1"/>
-    <col min="11" max="24" width="9.75" style="24" phonetic="1"/>
-    <col min="25" max="16384" width="9.75" style="24"/>
+    <col min="1" max="1" width="5.5" style="22" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="22" customWidth="1"/>
+    <col min="3" max="3" width="3.875" style="22" customWidth="1"/>
+    <col min="4" max="4" width="52.75" style="22" customWidth="1"/>
+    <col min="5" max="5" width="6.375" style="23" customWidth="1"/>
+    <col min="6" max="6" width="6.5" style="23" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="17.875" style="22" customWidth="1"/>
+    <col min="9" max="9" width="2.75" style="22" customWidth="1"/>
+    <col min="10" max="10" width="4.625" style="22" customWidth="1"/>
+    <col min="11" max="24" width="9.75" style="22" phonetic="1"/>
+    <col min="25" max="16384" width="9.75" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="27">
@@ -3386,17 +3411,20 @@
       <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:24" ht="35.25">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
       <c r="J2" s="2"/>
+      <c r="K2" s="83" t="s" ph="1">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" spans="1:24" ht="24">
       <c r="A3" s="9"/>
@@ -3409,13 +3437,13 @@
       <c r="H3" s="9"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:24" s="26" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A4" s="113" t="s">
+    <row r="4" spans="1:24" s="24" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A4" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="113"/>
+      <c r="B4" s="109"/>
       <c r="C4" s="11"/>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="122" t="s">
         <v>50</v>
       </c>
       <c r="E4" s="13"/>
@@ -3423,28 +3451,28 @@
       <c r="G4" s="14"/>
       <c r="H4" s="12"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="26" ph="1"/>
-      <c r="L4" s="26" ph="1"/>
-      <c r="M4" s="26" ph="1"/>
-      <c r="N4" s="26" ph="1"/>
-      <c r="O4" s="26" ph="1"/>
-      <c r="P4" s="26" ph="1"/>
-      <c r="Q4" s="26" ph="1"/>
-      <c r="R4" s="26" ph="1"/>
-      <c r="S4" s="26" ph="1"/>
-      <c r="T4" s="26" ph="1"/>
-      <c r="U4" s="26" ph="1"/>
-      <c r="V4" s="26" ph="1"/>
-      <c r="W4" s="26" ph="1"/>
-      <c r="X4" s="26" ph="1"/>
-    </row>
-    <row r="5" spans="1:24" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="115" t="s">
+      <c r="K4" s="24" ph="1"/>
+      <c r="L4" s="24" ph="1"/>
+      <c r="M4" s="24" ph="1"/>
+      <c r="N4" s="24" ph="1"/>
+      <c r="O4" s="24" ph="1"/>
+      <c r="P4" s="24" ph="1"/>
+      <c r="Q4" s="24" ph="1"/>
+      <c r="R4" s="24" ph="1"/>
+      <c r="S4" s="24" ph="1"/>
+      <c r="T4" s="24" ph="1"/>
+      <c r="U4" s="24" ph="1"/>
+      <c r="V4" s="24" ph="1"/>
+      <c r="W4" s="24" ph="1"/>
+      <c r="X4" s="24" ph="1"/>
+    </row>
+    <row r="5" spans="1:24" s="24" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="115"/>
+      <c r="B5" s="111"/>
       <c r="C5" s="15"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="123" t="s">
         <v>52</v>
       </c>
       <c r="E5" s="13"/>
@@ -3452,26 +3480,26 @@
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="26" ph="1"/>
-      <c r="L5" s="26" ph="1"/>
-      <c r="M5" s="26" ph="1"/>
-      <c r="N5" s="26" ph="1"/>
-      <c r="O5" s="26" ph="1"/>
-      <c r="P5" s="26" ph="1"/>
-      <c r="Q5" s="26" ph="1"/>
-      <c r="R5" s="26" ph="1"/>
-      <c r="S5" s="26" ph="1"/>
-      <c r="T5" s="26" ph="1"/>
-      <c r="U5" s="26" ph="1"/>
-      <c r="V5" s="26" ph="1"/>
-      <c r="W5" s="26" ph="1"/>
-      <c r="X5" s="26" ph="1"/>
+      <c r="K5" s="24" ph="1"/>
+      <c r="L5" s="24" ph="1"/>
+      <c r="M5" s="24" ph="1"/>
+      <c r="N5" s="24" ph="1"/>
+      <c r="O5" s="24" ph="1"/>
+      <c r="P5" s="24" ph="1"/>
+      <c r="Q5" s="24" ph="1"/>
+      <c r="R5" s="24" ph="1"/>
+      <c r="S5" s="24" ph="1"/>
+      <c r="T5" s="24" ph="1"/>
+      <c r="U5" s="24" ph="1"/>
+      <c r="V5" s="24" ph="1"/>
+      <c r="W5" s="24" ph="1"/>
+      <c r="X5" s="24" ph="1"/>
     </row>
     <row r="6" spans="1:24" ht="15" customHeight="1">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
       <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
+      <c r="D6" s="124"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="9"/>
@@ -3479,25 +3507,25 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="113"/>
+      <c r="B7" s="109"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="122" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="19"/>
+      <c r="G7" s="18"/>
       <c r="H7" s="9"/>
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:24" ht="15" customHeight="1">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="9" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="125" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="10"/>
@@ -3506,13 +3534,13 @@
       <c r="H8" s="9"/>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:24" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="113" t="s">
+    <row r="9" spans="1:24" s="24" customFormat="1" ht="15" customHeight="1">
+      <c r="A9" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="113"/>
+      <c r="B9" s="109"/>
       <c r="C9" s="11"/>
-      <c r="D9" s="22">
+      <c r="D9" s="126">
         <f>H40</f>
         <v>19800000</v>
       </c>
@@ -3521,28 +3549,28 @@
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="26" ph="1"/>
-      <c r="L9" s="26" ph="1"/>
-      <c r="M9" s="26" ph="1"/>
-      <c r="N9" s="26" ph="1"/>
-      <c r="O9" s="26" ph="1"/>
-      <c r="P9" s="26" ph="1"/>
-      <c r="Q9" s="26" ph="1"/>
-      <c r="R9" s="26" ph="1"/>
-      <c r="S9" s="26" ph="1"/>
-      <c r="T9" s="26" ph="1"/>
-      <c r="U9" s="26" ph="1"/>
-      <c r="V9" s="26" ph="1"/>
-      <c r="W9" s="26" ph="1"/>
-      <c r="X9" s="26" ph="1"/>
+      <c r="K9" s="24" ph="1"/>
+      <c r="L9" s="24" ph="1"/>
+      <c r="M9" s="24" ph="1"/>
+      <c r="N9" s="24" ph="1"/>
+      <c r="O9" s="24" ph="1"/>
+      <c r="P9" s="24" ph="1"/>
+      <c r="Q9" s="24" ph="1"/>
+      <c r="R9" s="24" ph="1"/>
+      <c r="S9" s="24" ph="1"/>
+      <c r="T9" s="24" ph="1"/>
+      <c r="U9" s="24" ph="1"/>
+      <c r="V9" s="24" ph="1"/>
+      <c r="W9" s="24" ph="1"/>
+      <c r="X9" s="24" ph="1"/>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1">
-      <c r="A10" s="113" t="s">
+      <c r="A10" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="113"/>
+      <c r="B10" s="109"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="28">
+      <c r="D10" s="127">
         <f>H40</f>
         <v>19800000</v>
       </c>
@@ -3552,38 +3580,38 @@
       <c r="H10" s="9"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:24" s="26" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="1:24" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="23"/>
+      <c r="G11" s="21"/>
       <c r="H11" s="12"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="26" ph="1"/>
-      <c r="L11" s="26" ph="1"/>
-      <c r="M11" s="26" ph="1"/>
-      <c r="N11" s="26" ph="1"/>
-      <c r="O11" s="26" ph="1"/>
-      <c r="P11" s="26" ph="1"/>
-      <c r="Q11" s="26" ph="1"/>
-      <c r="R11" s="26" ph="1"/>
-      <c r="S11" s="26" ph="1"/>
-      <c r="T11" s="26" ph="1"/>
-      <c r="U11" s="26" ph="1"/>
-      <c r="V11" s="26" ph="1"/>
-      <c r="W11" s="26" ph="1"/>
-      <c r="X11" s="26" ph="1"/>
+      <c r="K11" s="24" ph="1"/>
+      <c r="L11" s="24" ph="1"/>
+      <c r="M11" s="24" ph="1"/>
+      <c r="N11" s="24" ph="1"/>
+      <c r="O11" s="24" ph="1"/>
+      <c r="P11" s="24" ph="1"/>
+      <c r="Q11" s="24" ph="1"/>
+      <c r="R11" s="24" ph="1"/>
+      <c r="S11" s="24" ph="1"/>
+      <c r="T11" s="24" ph="1"/>
+      <c r="U11" s="24" ph="1"/>
+      <c r="V11" s="24" ph="1"/>
+      <c r="W11" s="24" ph="1"/>
+      <c r="X11" s="24" ph="1"/>
     </row>
     <row r="12" spans="1:24" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A12" s="90" t="s">
+      <c r="A12" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="89"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="85"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="9"/>
@@ -3592,56 +3620,56 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="26" customFormat="1" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A13" s="29" t="s">
+    <row r="13" spans="1:24" s="24" customFormat="1" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A13" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="111" t="s">
+      <c r="B13" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="77" t="s">
+      <c r="C13" s="108"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="78" t="s">
+      <c r="F13" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="77" t="s">
+      <c r="G13" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="79" t="s">
+      <c r="H13" s="75" t="s">
         <v>7</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="K13" s="26" ph="1"/>
-      <c r="L13" s="26" ph="1"/>
-      <c r="M13" s="26" ph="1"/>
-      <c r="N13" s="26" ph="1"/>
-      <c r="O13" s="26" ph="1"/>
-      <c r="P13" s="26" ph="1"/>
-      <c r="Q13" s="26" ph="1"/>
-      <c r="R13" s="26" ph="1"/>
-      <c r="S13" s="26" ph="1"/>
-      <c r="T13" s="26" ph="1"/>
-      <c r="U13" s="26" ph="1"/>
-      <c r="V13" s="26" ph="1"/>
-      <c r="W13" s="26" ph="1"/>
-      <c r="X13" s="26" ph="1"/>
+      <c r="K13" s="24" ph="1"/>
+      <c r="L13" s="24" ph="1"/>
+      <c r="M13" s="24" ph="1"/>
+      <c r="N13" s="24" ph="1"/>
+      <c r="O13" s="24" ph="1"/>
+      <c r="P13" s="24" ph="1"/>
+      <c r="Q13" s="24" ph="1"/>
+      <c r="R13" s="24" ph="1"/>
+      <c r="S13" s="24" ph="1"/>
+      <c r="T13" s="24" ph="1"/>
+      <c r="U13" s="24" ph="1"/>
+      <c r="V13" s="24" ph="1"/>
+      <c r="W13" s="24" ph="1"/>
+      <c r="X13" s="24" ph="1"/>
     </row>
     <row r="14" spans="1:24" ht="19.5" customHeight="1" thickTop="1">
-      <c r="A14" s="52"/>
-      <c r="B14" s="53" t="s">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="76" t="s">
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="72" t="s">
         <v>28</v>
       </c>
       <c r="J14" s="8" t="str">
@@ -3650,70 +3678,70 @@
       </c>
     </row>
     <row r="15" spans="1:24" ht="19.5" customHeight="1">
-      <c r="A15" s="58"/>
-      <c r="B15" s="64" t="s">
+      <c r="A15" s="54"/>
+      <c r="B15" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="65"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="59"/>
       <c r="J15" s="8" t="str">
         <f t="shared" ref="J15:J37" si="0">IF(A15&gt;0,A15,"")</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:24" ht="19.5" customHeight="1">
-      <c r="A16" s="58"/>
-      <c r="B16" s="59" t="s">
+      <c r="A16" s="54"/>
+      <c r="B16" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="97"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="93"/>
       <c r="J16" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="31"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="101"/>
-      <c r="H17" s="102"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="98"/>
       <c r="J17" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="34">
+      <c r="A18" s="30">
         <v>1</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="36" t="s">
+      <c r="B18" s="31"/>
+      <c r="C18" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="103"/>
-      <c r="E18" s="104">
+      <c r="D18" s="99"/>
+      <c r="E18" s="100">
         <v>2</v>
       </c>
-      <c r="F18" s="105" t="s">
+      <c r="F18" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="106">
+      <c r="G18" s="102">
         <v>9900000</v>
       </c>
-      <c r="H18" s="107">
+      <c r="H18" s="103">
         <f>E18*G18</f>
         <v>19800000</v>
       </c>
@@ -3723,479 +3751,479 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="34"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36" t="s">
+      <c r="A19" s="30"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="103"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="107"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="103"/>
       <c r="J19" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="34"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="36" t="s">
+      <c r="A20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="103"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="107"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="101"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="103"/>
       <c r="J20" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="34"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="107"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="103"/>
       <c r="J21" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36" t="s">
+      <c r="A22" s="30"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="41"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="37"/>
       <c r="J22" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="34"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="36" t="s">
+      <c r="A23" s="30"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="37" t="s">
+      <c r="D23" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="34">
         <v>2</v>
       </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="41"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="37"/>
       <c r="J23" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="34"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="36" t="s">
+      <c r="A24" s="30"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="34">
         <v>2</v>
       </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="41"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="37"/>
       <c r="J24" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="43"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="36" t="s">
+      <c r="A25" s="39"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="34">
         <v>2</v>
       </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="41"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="37"/>
       <c r="J25" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="34"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="36" t="s">
+      <c r="A26" s="30"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="D26" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="34">
         <v>2</v>
       </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="41"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="37"/>
       <c r="J26" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="34"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="36" t="s">
+      <c r="A27" s="30"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="38">
+      <c r="E27" s="34">
         <v>2</v>
       </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="37"/>
       <c r="J27" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="34"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="36" t="s">
+      <c r="A28" s="30"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="34">
         <v>2</v>
       </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="41"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="37"/>
       <c r="J28" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="34"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="36" t="s">
+      <c r="A29" s="30"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="37" t="s">
+      <c r="D29" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="38">
+      <c r="E29" s="34">
         <v>2</v>
       </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="41"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="37"/>
       <c r="J29" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="34"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36" t="s">
+      <c r="A30" s="30"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D30" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="34">
         <v>2</v>
       </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="41"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="37"/>
       <c r="J30" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="34"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="36" t="s">
+      <c r="A31" s="30"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D31" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="38">
+      <c r="E31" s="34">
         <v>2</v>
       </c>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="41"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="37"/>
       <c r="J31" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="34"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="41"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="37"/>
       <c r="J32" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="41"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="37"/>
       <c r="J33" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A34" s="34"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="41"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="37"/>
       <c r="J34" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A35" s="34"/>
-      <c r="B35" s="35"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="41"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="37"/>
       <c r="J35" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:12" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A36" s="44"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="51"/>
+      <c r="A36" s="40"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="47"/>
       <c r="J36" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:12" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A37" s="67"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="73"/>
-      <c r="H37" s="75"/>
+      <c r="A37" s="63"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="71"/>
       <c r="J37" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A38" s="108" t="s">
+      <c r="A38" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="109"/>
-      <c r="C38" s="109"/>
-      <c r="D38" s="109"/>
-      <c r="E38" s="109"/>
-      <c r="F38" s="109"/>
-      <c r="G38" s="110"/>
-      <c r="H38" s="74"/>
-      <c r="J38" s="91"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
+      <c r="B38" s="105"/>
+      <c r="C38" s="105"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="105"/>
+      <c r="F38" s="105"/>
+      <c r="G38" s="106"/>
+      <c r="H38" s="70"/>
+      <c r="J38" s="87"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
     </row>
     <row r="39" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A39" s="119" t="s">
+      <c r="A39" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="119"/>
-      <c r="C39" s="119"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="81"/>
-      <c r="J39" s="92"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
+      <c r="B39" s="115"/>
+      <c r="C39" s="115"/>
+      <c r="D39" s="115"/>
+      <c r="E39" s="115"/>
+      <c r="F39" s="116"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="77"/>
+      <c r="J39" s="88"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
     </row>
     <row r="40" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A40" s="123" t="s">
+      <c r="A40" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="123"/>
-      <c r="C40" s="123"/>
-      <c r="D40" s="123"/>
-      <c r="E40" s="123"/>
-      <c r="F40" s="124"/>
-      <c r="G40" s="80" t="s">
+      <c r="B40" s="119"/>
+      <c r="C40" s="119"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="83">
+      <c r="H40" s="79">
         <f>SUM(H14:H36)</f>
         <v>19800000</v>
       </c>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A41" s="82"/>
-      <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="85"/>
-      <c r="H41" s="86" t="s">
+      <c r="A41" s="78"/>
+      <c r="B41" s="80"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="82" t="s">
         <v>26</v>
       </c>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A42" s="121" t="s">
+      <c r="A42" s="117" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="121"/>
-      <c r="C42" s="122" t="s">
+      <c r="B42" s="117"/>
+      <c r="C42" s="118" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="122"/>
-      <c r="E42" s="121" t="s">
+      <c r="D42" s="118"/>
+      <c r="E42" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="F42" s="121"/>
-      <c r="G42" s="125" t="s">
+      <c r="F42" s="117"/>
+      <c r="G42" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="H42" s="116"/>
+      <c r="H42" s="112"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A43" s="121" t="s">
+      <c r="A43" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="121"/>
-      <c r="C43" s="122" t="s">
+      <c r="B43" s="117"/>
+      <c r="C43" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="122"/>
-      <c r="E43" s="121" t="s">
+      <c r="D43" s="118"/>
+      <c r="E43" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="F43" s="121"/>
-      <c r="G43" s="116" t="s">
+      <c r="F43" s="117"/>
+      <c r="G43" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="H43" s="116"/>
+      <c r="H43" s="112"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A44" s="121" t="s">
+      <c r="A44" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="B44" s="121"/>
-      <c r="C44" s="122" t="s">
+      <c r="B44" s="117"/>
+      <c r="C44" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="122"/>
-      <c r="E44" s="121" t="s">
+      <c r="D44" s="118"/>
+      <c r="E44" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="F44" s="121"/>
-      <c r="G44" s="116" t="s">
+      <c r="F44" s="117"/>
+      <c r="G44" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="H44" s="116"/>
+      <c r="H44" s="112"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A45" s="117"/>
-      <c r="B45" s="118"/>
-      <c r="C45" s="118"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="118"/>
-      <c r="F45" s="118"/>
-      <c r="G45" s="118"/>
-      <c r="H45" s="118"/>
+      <c r="A45" s="113"/>
+      <c r="B45" s="114"/>
+      <c r="C45" s="114"/>
+      <c r="D45" s="114"/>
+      <c r="E45" s="114"/>
+      <c r="F45" s="114"/>
+      <c r="G45" s="114"/>
+      <c r="H45" s="114"/>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:12" ht="24">
-      <c r="A46" s="87"/>
-      <c r="B46" s="87"/>
-      <c r="C46" s="87"/>
-      <c r="D46" s="87"/>
-      <c r="E46" s="88"/>
-      <c r="F46" s="88"/>
-      <c r="G46" s="87"/>
-      <c r="H46" s="87"/>
+      <c r="A46" s="83"/>
+      <c r="B46" s="83"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="84"/>
+      <c r="F46" s="84"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="83"/>
     </row>
     <row r="47" spans="1:12" ht="24">
-      <c r="A47" s="87"/>
-      <c r="B47" s="87"/>
-      <c r="C47" s="87"/>
-      <c r="D47" s="87"/>
-      <c r="E47" s="88"/>
-      <c r="F47" s="88"/>
-      <c r="G47" s="87"/>
-      <c r="H47" s="87"/>
+      <c r="A47" s="83"/>
+      <c r="B47" s="83"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="84"/>
+      <c r="F47" s="84"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="23">
